--- a/Projects/CmF_SHG_Women_Entrepreneurs/reports/excel_exports/Dausa_Survey_Analysis_All_In_One_Master.xlsx
+++ b/Projects/CmF_SHG_Women_Entrepreneurs/reports/excel_exports/Dausa_Survey_Analysis_All_In_One_Master.xlsx
@@ -890,23 +890,23 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>2253000</v>
+        <v>1621000</v>
       </c>
       <c r="F9" s="8">
         <f>IF(D9&gt;0, E9/D9, 0)</f>
         <v/>
       </c>
       <c r="G9" s="9" t="n">
-        <v>200000</v>
+        <v>120000</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>175000</v>
+        <v>150000</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>1139000</v>
+        <v>729000</v>
       </c>
       <c r="J9" s="9" t="n">
         <v>0</v>
@@ -915,16 +915,16 @@
         <v>0</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>30000</v>
+        <v>10000</v>
       </c>
       <c r="M9" s="9" t="n">
         <v>0</v>
       </c>
       <c r="N9" s="9" t="n">
-        <v>309000</v>
+        <v>252000</v>
       </c>
       <c r="O9" s="9" t="n">
-        <v>320000</v>
+        <v>280000</v>
       </c>
       <c r="P9" s="9" t="n">
         <v>80000</v>
@@ -942,7 +942,7 @@
         <v>0</v>
       </c>
       <c r="U9" s="10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -1022,23 +1022,23 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>73000</v>
+        <v>0</v>
       </c>
       <c r="F11" s="8">
         <f>IF(D11&gt;0, E11/D11, 0)</f>
         <v/>
       </c>
       <c r="G11" s="9" t="n">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="H11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>31000</v>
+        <v>0</v>
       </c>
       <c r="J11" s="9" t="n">
         <v>0</v>
@@ -1056,7 +1056,7 @@
         <v>0</v>
       </c>
       <c r="O11" s="9" t="n">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="P11" s="9" t="n">
         <v>0</v>
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="U11" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -2919,7 +2919,7 @@
         </is>
       </c>
       <c r="D45" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E45" s="14" t="n">
         <v>1</v>
@@ -2931,7 +2931,7 @@
         <v>2</v>
       </c>
       <c r="H45" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46">
@@ -2977,13 +2977,13 @@
         <v>0</v>
       </c>
       <c r="F47" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G47" s="14" t="n">
         <v>0</v>
       </c>
       <c r="H47" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -6516,22 +6516,22 @@
         </is>
       </c>
       <c r="D4" s="18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E4" s="25" t="n">
-        <v>2253000</v>
+        <v>1621000</v>
       </c>
       <c r="F4" s="26" t="n">
-        <v>281625</v>
+        <v>231571.4285714286</v>
       </c>
       <c r="G4" s="25" t="n">
-        <v>200000</v>
+        <v>120000</v>
       </c>
       <c r="H4" s="25" t="n">
-        <v>175000</v>
+        <v>150000</v>
       </c>
       <c r="I4" s="25" t="n">
-        <v>1139000</v>
+        <v>729000</v>
       </c>
       <c r="J4" s="26" t="n">
         <v>0</v>
@@ -6540,16 +6540,16 @@
         <v>0</v>
       </c>
       <c r="L4" s="25" t="n">
-        <v>30000</v>
+        <v>10000</v>
       </c>
       <c r="M4" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N4" s="25" t="n">
-        <v>309000</v>
+        <v>252000</v>
       </c>
       <c r="O4" s="25" t="n">
-        <v>320000</v>
+        <v>280000</v>
       </c>
       <c r="P4" s="25" t="n">
         <v>80000</v>
@@ -6567,7 +6567,7 @@
         <v>0</v>
       </c>
       <c r="U4" s="18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -6645,23 +6645,23 @@
           <t>Apparel/fabric</t>
         </is>
       </c>
-      <c r="D6" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="25" t="n">
-        <v>73000</v>
+      <c r="D6" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="F6" s="26" t="n">
-        <v>73000</v>
-      </c>
-      <c r="G6" s="25" t="n">
-        <v>12000</v>
+        <v>0</v>
+      </c>
+      <c r="G6" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="H6" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="25" t="n">
-        <v>31000</v>
+      <c r="I6" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="J6" s="26" t="n">
         <v>0</v>
@@ -6678,8 +6678,8 @@
       <c r="N6" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="O6" s="25" t="n">
-        <v>30000</v>
+      <c r="O6" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="P6" s="26" t="n">
         <v>0</v>
@@ -6696,8 +6696,8 @@
       <c r="T6" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="U6" s="18" t="n">
-        <v>1</v>
+      <c r="U6" s="20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -9583,7 +9583,7 @@
         </is>
       </c>
       <c r="D5" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" s="18" t="n">
         <v>1</v>
@@ -9595,7 +9595,7 @@
         <v>2</v>
       </c>
       <c r="H5" s="18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -9640,14 +9640,14 @@
       <c r="E7" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="18" t="n">
-        <v>1</v>
+      <c r="F7" s="20" t="n">
+        <v>0</v>
       </c>
       <c r="G7" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="18" t="n">
-        <v>1</v>
+      <c r="H7" s="20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">

--- a/Projects/CmF_SHG_Women_Entrepreneurs/reports/excel_exports/Dausa_Survey_Analysis_All_In_One_Master.xlsx
+++ b/Projects/CmF_SHG_Women_Entrepreneurs/reports/excel_exports/Dausa_Survey_Analysis_All_In_One_Master.xlsx
@@ -1540,7 +1540,7 @@
         <v>0</v>
       </c>
       <c r="U18" s="10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
